--- a/template/u4FCPv2/KUP/sitcp/sources/wishbone/wb_reg/reg_table.xlsx
+++ b/template/u4FCPv2/KUP/sitcp/sources/wishbone/wb_reg/reg_table.xlsx
@@ -8,7 +8,7 @@
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="reg" sheetId="1" state="visible" r:id="rId2"/>
+    <sheet name="reg" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="82">
   <si>
     <t xml:space="preserve">block name</t>
   </si>
@@ -31,6 +31,15 @@
     <t xml:space="preserve">byte size</t>
   </si>
   <si>
+    <t xml:space="preserve">bus width</t>
+  </si>
+  <si>
+    <t xml:space="preserve">protocol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wishbone</t>
+  </si>
+  <si>
     <t xml:space="preserve">name</t>
   </si>
   <si>
@@ -73,31 +82,190 @@
     <t xml:space="preserve">default: 0x0</t>
   </si>
   <si>
-    <t xml:space="preserve">Synthesis date: Hour, binary-coded decimal expression</t>
+    <t xml:space="preserve">Synthesis date - hour, BCD (00-23)</t>
   </si>
   <si>
     <t xml:space="preserve">date</t>
   </si>
   <si>
-    <t xml:space="preserve">Synthesis date: Date</t>
+    <t xml:space="preserve">Synthesis date - day of month, BCD (01-31)</t>
   </si>
   <si>
     <t xml:space="preserve">month</t>
   </si>
   <si>
-    <t xml:space="preserve">Synthesis date: Month</t>
+    <t xml:space="preserve">Synthesis date - month, BCD (01-12)</t>
   </si>
   <si>
     <t xml:space="preserve">year</t>
   </si>
   <si>
-    <t xml:space="preserve">Synthesis date: Last two figures of A.D.</t>
+    <t xml:space="preserve">Synthesis date - two-digit year, BCD (00-99); century implied</t>
   </si>
   <si>
     <t xml:space="preserve">syn_ver</t>
   </si>
   <si>
-    <t xml:space="preserve">Firmware Version</t>
+    <t xml:space="preserve">Firmware version (auto update at synthesis)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sys_rst</t>
+  </si>
+  <si>
+    <t xml:space="preserve">usr_rst</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">w1trg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Write 1 to generate a reset pulse for the user logic; write 0 has no effect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ddr_rst</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Write 1 to generate a reset pulse for the DDR; write 0 has no effect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mod_rst</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Write 1 to generate a reset pulse for the front-end modules; write 0 has no effect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">qsfp_rst</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Write 1 to generate a reset pulse for the QSFP; write 0 has no effect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sys_sta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">clk_lock</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 = MMCM not locked; 1 = MMCM locked</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sys_sta_lch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rotrg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Latched copy of sys_sta.clk_lock. Sticky: cleared by reading this register</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mod_sta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">temp_alm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 = Normal; 1 = Over-temperature alarm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lv_alm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 = Normal; 1 = Low-voltage over-current alarm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hv_alm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 = Normal; 1 = High-voltage over-current alarm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">qsfp_alm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 = Normal; 1 = QSFP28 alarm (module fault or critical host status)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">qsfp_prs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 = QSFP module absent; 1 = QSFP module present</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mod_sta_lch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Latched copy of mod_sta.temp_alm. Sticky: cleared by reading this register</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Latched copy of mod_sta.lv_alm. Sticky: cleared by reading this register</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Latched copy of mod_sta.hv_alm. Sticky: cleared by reading this register</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Latched copy of mod_sta.qsfp_alm. Sticky: cleared by reading this register</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Latched copy of mod_sta.qsfp_prs. Sticky: cleared by reading this register</t>
+  </si>
+  <si>
+    <t xml:space="preserve">clk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ext_en</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rw</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 = Use on-board/local clock; 1 = Use external clock from AMC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">enable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 = Module power OFF; 1 = Module power ON</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ot_auto_off</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 = Normal; 1 = Auto power OFF on over-temperature</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">stop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">default: 0x1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 = High voltage ON; 1 = High-voltage emergency shutdown (safe default: 1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">oc_auto_off</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 = Normal; 1 = Auto power OFF on over-current</t>
+  </si>
+  <si>
+    <t xml:space="preserve">qsfp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lpmode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 = Normal (Full-Power) mode; 1 = Low-Power mode</t>
   </si>
 </sst>
 </file>
@@ -140,7 +308,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="13">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
@@ -150,6 +318,83 @@
     </border>
     <border diagonalUp="false" diagonalDown="false">
       <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin"/>
+      <right/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin"/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right style="thin"/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin"/>
+      <right/>
+      <top/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right style="thin"/>
+      <top/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin"/>
+      <right/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
@@ -181,28 +426,156 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="38">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="11" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="11" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="11" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -218,8 +591,114 @@
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office">
+  <a:themeElements>
+    <a:clrScheme name="LibreOffice">
+      <a:dk1>
+        <a:srgbClr val="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:srgbClr val="ffffff"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="000000"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="ffffff"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="18a303"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="0369a3"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="a33e03"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="8e03a3"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="c99c00"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="c9211e"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0000ee"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="551a8b"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme>
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
@@ -227,22 +706,22 @@
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="18.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="11.51"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="5.81"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="5.81"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="5.76"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="10.51"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="16.25"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="11.63"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="7.12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="11.38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="2" width="11.38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="8.42"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="7.61"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="53.26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="2" width="80.31"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="18.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="2" t="s">
         <v>1</v>
       </c>
     </row>
@@ -250,176 +729,673 @@
       <c r="B2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="0" t="n">
+      <c r="C2" s="2" t="n">
         <v>256</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="2" t="s">
+    <row r="3" customFormat="false" ht="18.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C3" s="2" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="18.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="C4" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="2" t="s">
+    </row>
+    <row r="6" customFormat="false" ht="18.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="F4" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="G4" s="2" t="s">
+      <c r="C6" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="D6" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F6" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="I4" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J4" s="2" t="s">
+      <c r="G6" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H6" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K4" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="L4" s="3" t="s">
+      <c r="I6" s="4" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="2" t="s">
+      <c r="J6" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2" t="s">
+      <c r="K6" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="L6" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="H5" s="2" t="s">
+    </row>
+    <row r="7" customFormat="false" ht="18.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="I5" s="3" t="s">
+      <c r="C7" s="6"/>
+      <c r="D7" s="6"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="J5" s="2"/>
-      <c r="K5" s="2"/>
-      <c r="L5" s="3" t="s">
+      <c r="G7" s="7" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="4"/>
-      <c r="C6" s="5"/>
-      <c r="D6" s="5"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="2" t="s">
+      <c r="H7" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="G6" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="J6" s="4"/>
-      <c r="K6" s="4"/>
-      <c r="L6" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="4"/>
-      <c r="C7" s="5"/>
-      <c r="D7" s="5"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="2" t="s">
+      <c r="I7" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="J7" s="7"/>
+      <c r="K7" s="7"/>
+      <c r="L7" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="G7" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H7" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="J7" s="4"/>
-      <c r="K7" s="4"/>
-      <c r="L7" s="3" t="s">
+    </row>
+    <row r="8" customFormat="false" ht="18.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="9"/>
+      <c r="C8" s="10"/>
+      <c r="D8" s="10"/>
+      <c r="E8" s="11"/>
+      <c r="F8" s="12" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="4"/>
-      <c r="C8" s="5"/>
-      <c r="D8" s="5"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="2" t="s">
+      <c r="G8" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="H8" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="I8" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="J8" s="11"/>
+      <c r="K8" s="11"/>
+      <c r="L8" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="G8" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H8" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="J8" s="4"/>
-      <c r="K8" s="4"/>
-      <c r="L8" s="3" t="s">
+    </row>
+    <row r="9" customFormat="false" ht="18.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="9"/>
+      <c r="C9" s="10"/>
+      <c r="D9" s="10"/>
+      <c r="E9" s="11"/>
+      <c r="F9" s="12" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="2" t="s">
+      <c r="G9" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="H9" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="I9" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="J9" s="11"/>
+      <c r="K9" s="11"/>
+      <c r="L9" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="J9" s="2"/>
-      <c r="K9" s="2"/>
-      <c r="L9" s="5" t="s">
+    </row>
+    <row r="10" customFormat="false" ht="18.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B10" s="15"/>
+      <c r="C10" s="16"/>
+      <c r="D10" s="16"/>
+      <c r="E10" s="17"/>
+      <c r="F10" s="18" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="1048501" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048502" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048503" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048504" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048505" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048506" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048507" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048508" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048509" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048510" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048511" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048512" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048513" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048514" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+      <c r="G10" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="H10" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="I10" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="J10" s="17"/>
+      <c r="K10" s="17"/>
+      <c r="L10" s="20" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="18.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B11" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11" s="22"/>
+      <c r="D11" s="22"/>
+      <c r="E11" s="23"/>
+      <c r="F11" s="23"/>
+      <c r="G11" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="H11" s="23" t="s">
+        <v>18</v>
+      </c>
+      <c r="I11" s="24" t="s">
+        <v>19</v>
+      </c>
+      <c r="J11" s="23"/>
+      <c r="K11" s="23"/>
+      <c r="L11" s="25" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="18.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B12" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C12" s="26"/>
+      <c r="D12" s="26"/>
+      <c r="E12" s="27"/>
+      <c r="F12" s="27" t="s">
+        <v>30</v>
+      </c>
+      <c r="G12" s="27" t="s">
+        <v>31</v>
+      </c>
+      <c r="H12" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="I12" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="J12" s="27"/>
+      <c r="K12" s="27"/>
+      <c r="L12" s="8" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="18.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B13" s="28"/>
+      <c r="C13" s="16"/>
+      <c r="D13" s="16"/>
+      <c r="E13" s="17"/>
+      <c r="F13" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="G13" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="H13" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="I13" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="J13" s="17"/>
+      <c r="K13" s="17"/>
+      <c r="L13" s="20" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="18.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B14" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C14" s="26"/>
+      <c r="D14" s="26"/>
+      <c r="E14" s="27"/>
+      <c r="F14" s="29" t="s">
+        <v>36</v>
+      </c>
+      <c r="G14" s="27" t="s">
+        <v>31</v>
+      </c>
+      <c r="H14" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="I14" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="J14" s="27"/>
+      <c r="K14" s="27"/>
+      <c r="L14" s="8" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="18.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B15" s="28"/>
+      <c r="C15" s="16"/>
+      <c r="D15" s="16"/>
+      <c r="E15" s="17"/>
+      <c r="F15" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="G15" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="H15" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="I15" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="J15" s="17"/>
+      <c r="K15" s="17"/>
+      <c r="L15" s="20" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="18.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B16" s="30" t="s">
+        <v>40</v>
+      </c>
+      <c r="C16" s="22"/>
+      <c r="D16" s="22"/>
+      <c r="E16" s="31"/>
+      <c r="F16" s="22" t="s">
+        <v>41</v>
+      </c>
+      <c r="G16" s="31" t="s">
+        <v>31</v>
+      </c>
+      <c r="H16" s="31" t="s">
+        <v>42</v>
+      </c>
+      <c r="I16" s="24" t="s">
+        <v>19</v>
+      </c>
+      <c r="J16" s="31"/>
+      <c r="K16" s="31"/>
+      <c r="L16" s="25" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="18.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B17" s="30" t="s">
+        <v>44</v>
+      </c>
+      <c r="C17" s="22"/>
+      <c r="D17" s="22"/>
+      <c r="E17" s="31"/>
+      <c r="F17" s="22" t="s">
+        <v>41</v>
+      </c>
+      <c r="G17" s="31" t="s">
+        <v>31</v>
+      </c>
+      <c r="H17" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="I17" s="24" t="s">
+        <v>19</v>
+      </c>
+      <c r="J17" s="31"/>
+      <c r="K17" s="31"/>
+      <c r="L17" s="25" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="22.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B18" s="32" t="s">
+        <v>47</v>
+      </c>
+      <c r="C18" s="26"/>
+      <c r="D18" s="26"/>
+      <c r="E18" s="27"/>
+      <c r="F18" s="27" t="s">
+        <v>48</v>
+      </c>
+      <c r="G18" s="27" t="s">
+        <v>31</v>
+      </c>
+      <c r="H18" s="26" t="s">
+        <v>42</v>
+      </c>
+      <c r="I18" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="J18" s="27"/>
+      <c r="K18" s="27"/>
+      <c r="L18" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="20.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B19" s="33"/>
+      <c r="F19" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="I19" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="L19" s="14" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="22.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B20" s="33"/>
+      <c r="F20" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="I20" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="L20" s="14" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="26.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B21" s="33"/>
+      <c r="F21" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="I21" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="L21" s="14" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="20.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B22" s="34"/>
+      <c r="C22" s="16"/>
+      <c r="D22" s="35"/>
+      <c r="E22" s="17"/>
+      <c r="F22" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="G22" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="H22" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="I22" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="J22" s="16"/>
+      <c r="K22" s="16"/>
+      <c r="L22" s="20" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="18.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B23" s="32" t="s">
+        <v>58</v>
+      </c>
+      <c r="C23" s="26"/>
+      <c r="D23" s="26"/>
+      <c r="E23" s="26"/>
+      <c r="F23" s="27" t="s">
+        <v>48</v>
+      </c>
+      <c r="G23" s="27" t="s">
+        <v>31</v>
+      </c>
+      <c r="H23" s="26" t="s">
+        <v>45</v>
+      </c>
+      <c r="I23" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="J23" s="27"/>
+      <c r="K23" s="27"/>
+      <c r="L23" s="8" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="18.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B24" s="36"/>
+      <c r="E24" s="2"/>
+      <c r="F24" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="I24" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="L24" s="14" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="18.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B25" s="36"/>
+      <c r="E25" s="2"/>
+      <c r="F25" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="I25" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="L25" s="14" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="18.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B26" s="36"/>
+      <c r="E26" s="2"/>
+      <c r="F26" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="I26" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="L26" s="14" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="18.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B27" s="36"/>
+      <c r="E27" s="2"/>
+      <c r="F27" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="I27" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="L27" s="14" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="19.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B28" s="30" t="s">
+        <v>64</v>
+      </c>
+      <c r="C28" s="22"/>
+      <c r="D28" s="37"/>
+      <c r="E28" s="22"/>
+      <c r="F28" s="22" t="s">
+        <v>65</v>
+      </c>
+      <c r="G28" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="H28" s="22" t="s">
+        <v>66</v>
+      </c>
+      <c r="I28" s="24" t="s">
+        <v>19</v>
+      </c>
+      <c r="J28" s="23"/>
+      <c r="K28" s="23"/>
+      <c r="L28" s="25" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="18.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B29" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C29" s="26"/>
+      <c r="D29" s="26"/>
+      <c r="E29" s="27"/>
+      <c r="F29" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G29" s="27" t="s">
+        <v>31</v>
+      </c>
+      <c r="H29" s="27" t="s">
+        <v>66</v>
+      </c>
+      <c r="I29" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="J29" s="27"/>
+      <c r="K29" s="27"/>
+      <c r="L29" s="8" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="23.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B30" s="28"/>
+      <c r="C30" s="16"/>
+      <c r="D30" s="16"/>
+      <c r="E30" s="17"/>
+      <c r="F30" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="G30" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="H30" s="17" t="s">
+        <v>66</v>
+      </c>
+      <c r="I30" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="J30" s="17"/>
+      <c r="K30" s="17"/>
+      <c r="L30" s="20" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="20.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B31" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="C31" s="26"/>
+      <c r="D31" s="26"/>
+      <c r="E31" s="27"/>
+      <c r="F31" s="27" t="s">
+        <v>74</v>
+      </c>
+      <c r="G31" s="27" t="s">
+        <v>31</v>
+      </c>
+      <c r="H31" s="27" t="s">
+        <v>66</v>
+      </c>
+      <c r="I31" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="J31" s="27"/>
+      <c r="K31" s="27"/>
+      <c r="L31" s="8" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="21.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B32" s="28"/>
+      <c r="C32" s="16"/>
+      <c r="D32" s="16"/>
+      <c r="E32" s="17"/>
+      <c r="F32" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="G32" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="H32" s="17" t="s">
+        <v>66</v>
+      </c>
+      <c r="I32" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="J32" s="17"/>
+      <c r="K32" s="17"/>
+      <c r="L32" s="20" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="24.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B33" s="21" t="s">
+        <v>79</v>
+      </c>
+      <c r="C33" s="22"/>
+      <c r="D33" s="22"/>
+      <c r="E33" s="31"/>
+      <c r="F33" s="31" t="s">
+        <v>80</v>
+      </c>
+      <c r="G33" s="31" t="s">
+        <v>31</v>
+      </c>
+      <c r="H33" s="31" t="s">
+        <v>66</v>
+      </c>
+      <c r="I33" s="24" t="s">
+        <v>19</v>
+      </c>
+      <c r="J33" s="31"/>
+      <c r="K33" s="31"/>
+      <c r="L33" s="25" t="s">
+        <v>81</v>
+      </c>
+    </row>
     <row r="1048515" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048516" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048517" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
